--- a/artfynd/A 24660-2026 artfynd.xlsx
+++ b/artfynd/A 24660-2026 artfynd.xlsx
@@ -2064,10 +2064,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134374890</v>
+        <v>134374928</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>80475</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2075,21 +2075,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>390089</v>
+        <v>390214</v>
       </c>
       <c r="R16" t="n">
-        <v>7042129</v>
+        <v>7042215</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,11 +2135,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2166,10 +2161,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134374928</v>
+        <v>134374940</v>
       </c>
       <c r="B17" t="n">
-        <v>80475</v>
+        <v>79359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2177,21 +2172,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2201,10 +2196,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>390214</v>
+        <v>390093</v>
       </c>
       <c r="R17" t="n">
-        <v>7042215</v>
+        <v>7042070</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2263,10 +2258,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134374940</v>
+        <v>134374890</v>
       </c>
       <c r="B18" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2274,21 +2269,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2298,10 +2293,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>390093</v>
+        <v>390089</v>
       </c>
       <c r="R18" t="n">
-        <v>7042070</v>
+        <v>7042129</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2334,6 +2329,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3636,7 +3636,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134374867</v>
+        <v>134374877</v>
       </c>
       <c r="B32" t="n">
         <v>57975</v>
@@ -3671,10 +3671,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>390338</v>
+        <v>390321</v>
       </c>
       <c r="R32" t="n">
-        <v>7042119</v>
+        <v>7042303</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3738,7 +3738,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134374877</v>
+        <v>134374867</v>
       </c>
       <c r="B33" t="n">
         <v>57975</v>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>390321</v>
+        <v>390338</v>
       </c>
       <c r="R33" t="n">
-        <v>7042303</v>
+        <v>7042119</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3840,10 +3840,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134374883</v>
+        <v>134374931</v>
       </c>
       <c r="B34" t="n">
-        <v>57975</v>
+        <v>80474</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3851,21 +3851,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3875,10 +3875,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>390314</v>
+        <v>390480</v>
       </c>
       <c r="R34" t="n">
-        <v>7042226</v>
+        <v>7042339</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3911,11 +3911,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3942,10 +3937,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134374931</v>
+        <v>134374883</v>
       </c>
       <c r="B35" t="n">
-        <v>80474</v>
+        <v>57975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3953,21 +3948,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3977,10 +3972,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>390480</v>
+        <v>390314</v>
       </c>
       <c r="R35" t="n">
-        <v>7042339</v>
+        <v>7042226</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4013,6 +4008,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4251,32 +4251,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134374923</v>
+        <v>134374925</v>
       </c>
       <c r="B38" t="n">
-        <v>99203</v>
+        <v>80475</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>390426</v>
+        <v>390411</v>
       </c>
       <c r="R38" t="n">
-        <v>7042147</v>
+        <v>7042114</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4348,32 +4348,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134374874</v>
+        <v>134374923</v>
       </c>
       <c r="B39" t="n">
-        <v>57975</v>
+        <v>99203</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4383,10 +4383,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>390364</v>
+        <v>390426</v>
       </c>
       <c r="R39" t="n">
-        <v>7042343</v>
+        <v>7042147</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4419,11 +4419,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4450,10 +4445,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134374925</v>
+        <v>134374875</v>
       </c>
       <c r="B40" t="n">
-        <v>80475</v>
+        <v>57975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4461,21 +4456,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4485,10 +4480,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>390411</v>
+        <v>390409</v>
       </c>
       <c r="R40" t="n">
-        <v>7042114</v>
+        <v>7042310</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4521,6 +4516,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4547,7 +4547,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134374875</v>
+        <v>134374874</v>
       </c>
       <c r="B41" t="n">
         <v>57975</v>
@@ -4582,10 +4582,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>390409</v>
+        <v>390364</v>
       </c>
       <c r="R41" t="n">
-        <v>7042310</v>
+        <v>7042343</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4751,32 +4751,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134374930</v>
+        <v>134374926</v>
       </c>
       <c r="B43" t="n">
-        <v>92392</v>
+        <v>80475</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>390513</v>
+        <v>390354</v>
       </c>
       <c r="R43" t="n">
-        <v>7042404</v>
+        <v>7042406</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4958,32 +4958,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134374926</v>
+        <v>134374930</v>
       </c>
       <c r="B45" t="n">
-        <v>80475</v>
+        <v>92392</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>1209</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>390354</v>
+        <v>390513</v>
       </c>
       <c r="R45" t="n">
-        <v>7042406</v>
+        <v>7042404</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5259,7 +5259,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134374878</v>
+        <v>134374870</v>
       </c>
       <c r="B48" t="n">
         <v>57975</v>
@@ -5294,10 +5294,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>390326</v>
+        <v>390368</v>
       </c>
       <c r="R48" t="n">
-        <v>7042294</v>
+        <v>7041804</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5361,32 +5361,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134374870</v>
+        <v>134374857</v>
       </c>
       <c r="B49" t="n">
-        <v>57975</v>
+        <v>92185</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>390368</v>
+        <v>390383</v>
       </c>
       <c r="R49" t="n">
-        <v>7041804</v>
+        <v>7042192</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5432,11 +5432,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5463,32 +5458,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134374857</v>
+        <v>134374878</v>
       </c>
       <c r="B50" t="n">
-        <v>92185</v>
+        <v>57975</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5498,10 +5493,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>390383</v>
+        <v>390326</v>
       </c>
       <c r="R50" t="n">
-        <v>7042192</v>
+        <v>7042294</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5534,6 +5529,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5968,10 +5968,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134374885</v>
+        <v>134374936</v>
       </c>
       <c r="B55" t="n">
-        <v>57975</v>
+        <v>91960</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5979,21 +5979,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>390325</v>
+        <v>390274</v>
       </c>
       <c r="R55" t="n">
-        <v>7042168</v>
+        <v>7042048</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6041,17 +6041,13 @@
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6070,10 +6066,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134374936</v>
+        <v>134374885</v>
       </c>
       <c r="B56" t="n">
-        <v>91960</v>
+        <v>57975</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6081,21 +6077,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6105,10 +6101,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>390274</v>
+        <v>390325</v>
       </c>
       <c r="R56" t="n">
-        <v>7042048</v>
+        <v>7042168</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6143,13 +6139,17 @@
           <t>2026-06-12</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24660-2026 artfynd.xlsx
+++ b/artfynd/A 24660-2026 artfynd.xlsx
@@ -1064,7 +1064,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134374865</v>
+        <v>134374889</v>
       </c>
       <c r="B6" t="n">
         <v>57975</v>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>390261</v>
+        <v>390050</v>
       </c>
       <c r="R6" t="n">
-        <v>7042085</v>
+        <v>7042163</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,7 +1166,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134374889</v>
+        <v>134374865</v>
       </c>
       <c r="B7" t="n">
         <v>57975</v>
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>390050</v>
+        <v>390261</v>
       </c>
       <c r="R7" t="n">
-        <v>7042163</v>
+        <v>7042085</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,7 +1271,7 @@
         <v>134374860</v>
       </c>
       <c r="B8" t="n">
-        <v>92185</v>
+        <v>92192</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>134374858</v>
       </c>
       <c r="B9" t="n">
-        <v>92185</v>
+        <v>92192</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>134374929</v>
       </c>
       <c r="B12" t="n">
-        <v>80475</v>
+        <v>80482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>134374935</v>
       </c>
       <c r="B14" t="n">
-        <v>91956</v>
+        <v>91963</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         <v>134374928</v>
       </c>
       <c r="B16" t="n">
-        <v>80475</v>
+        <v>80482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>134374940</v>
       </c>
       <c r="B17" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2360,53 +2360,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134374864</v>
+        <v>134374942</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>92682</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>390255</v>
+        <v>390101</v>
       </c>
       <c r="R19" t="n">
-        <v>7042088</v>
+        <v>7041912</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2439,11 +2431,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Senare års bohål, ca 4,5m upp i död gran. Finns ytterligare 3 äldre bohål i samma träd, troligen av tretå.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2470,45 +2457,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134374942</v>
+        <v>134374864</v>
       </c>
       <c r="B20" t="n">
-        <v>92675</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>390101</v>
+        <v>390255</v>
       </c>
       <c r="R20" t="n">
-        <v>7041912</v>
+        <v>7042088</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2541,6 +2536,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Senare års bohål, ca 4,5m upp i död gran. Finns ytterligare 3 äldre bohål i samma träd, troligen av tretå.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3348,7 +3348,7 @@
         <v>134374856</v>
       </c>
       <c r="B29" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         <v>134374859</v>
       </c>
       <c r="B30" t="n">
-        <v>92185</v>
+        <v>92192</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3539,32 +3539,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134374934</v>
+        <v>134374877</v>
       </c>
       <c r="B31" t="n">
-        <v>99085</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>390426</v>
+        <v>390321</v>
       </c>
       <c r="R31" t="n">
-        <v>7042146</v>
+        <v>7042303</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3610,6 +3610,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3636,7 +3641,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134374877</v>
+        <v>134374867</v>
       </c>
       <c r="B32" t="n">
         <v>57975</v>
@@ -3671,10 +3676,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>390321</v>
+        <v>390338</v>
       </c>
       <c r="R32" t="n">
-        <v>7042303</v>
+        <v>7042119</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3711,7 +3716,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3738,32 +3743,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134374867</v>
+        <v>134374934</v>
       </c>
       <c r="B33" t="n">
-        <v>57975</v>
+        <v>99092</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3773,10 +3778,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>390338</v>
+        <v>390426</v>
       </c>
       <c r="R33" t="n">
-        <v>7042119</v>
+        <v>7042146</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3809,11 +3814,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3843,7 +3843,7 @@
         <v>134374931</v>
       </c>
       <c r="B34" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>134374925</v>
       </c>
       <c r="B38" t="n">
-        <v>80475</v>
+        <v>80482</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4348,32 +4348,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134374923</v>
+        <v>134374875</v>
       </c>
       <c r="B39" t="n">
-        <v>99203</v>
+        <v>57975</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4383,10 +4383,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>390426</v>
+        <v>390409</v>
       </c>
       <c r="R39" t="n">
-        <v>7042147</v>
+        <v>7042310</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4419,6 +4419,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4445,32 +4450,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134374875</v>
+        <v>134374923</v>
       </c>
       <c r="B40" t="n">
-        <v>57975</v>
+        <v>99210</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4480,10 +4485,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>390409</v>
+        <v>390426</v>
       </c>
       <c r="R40" t="n">
-        <v>7042310</v>
+        <v>7042147</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4516,11 +4521,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4754,7 +4754,7 @@
         <v>134374926</v>
       </c>
       <c r="B43" t="n">
-        <v>80475</v>
+        <v>80482</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4848,53 +4848,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134374873</v>
+        <v>134374930</v>
       </c>
       <c r="B44" t="n">
-        <v>57975</v>
+        <v>92399</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>390461</v>
+        <v>390513</v>
       </c>
       <c r="R44" t="n">
-        <v>7042459</v>
+        <v>7042404</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4927,11 +4919,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Bohål, ca 1,7m upp i granhögstubbe</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4958,45 +4945,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134374930</v>
+        <v>134374873</v>
       </c>
       <c r="B45" t="n">
-        <v>92392</v>
+        <v>57975</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>390513</v>
+        <v>390461</v>
       </c>
       <c r="R45" t="n">
-        <v>7042404</v>
+        <v>7042459</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5029,6 +5024,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Bohål, ca 1,7m upp i granhögstubbe</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5259,32 +5259,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134374870</v>
+        <v>134374857</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>92192</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5294,10 +5294,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>390368</v>
+        <v>390383</v>
       </c>
       <c r="R48" t="n">
-        <v>7041804</v>
+        <v>7042192</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5330,11 +5330,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5361,32 +5356,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134374857</v>
+        <v>134374878</v>
       </c>
       <c r="B49" t="n">
-        <v>92185</v>
+        <v>57975</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5396,10 +5391,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>390383</v>
+        <v>390326</v>
       </c>
       <c r="R49" t="n">
-        <v>7042192</v>
+        <v>7042294</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5432,6 +5427,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5458,7 +5458,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134374878</v>
+        <v>134374870</v>
       </c>
       <c r="B50" t="n">
         <v>57975</v>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>390326</v>
+        <v>390368</v>
       </c>
       <c r="R50" t="n">
-        <v>7042294</v>
+        <v>7041804</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5533,7 +5533,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5662,7 +5662,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134374863</v>
+        <v>134374882</v>
       </c>
       <c r="B52" t="n">
         <v>57975</v>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>390316</v>
+        <v>390307</v>
       </c>
       <c r="R52" t="n">
-        <v>7041877</v>
+        <v>7042259</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5764,7 +5764,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134374882</v>
+        <v>134374863</v>
       </c>
       <c r="B53" t="n">
         <v>57975</v>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>390307</v>
+        <v>390316</v>
       </c>
       <c r="R53" t="n">
-        <v>7042259</v>
+        <v>7041877</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5971,7 +5971,7 @@
         <v>134374936</v>
       </c>
       <c r="B55" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>134374941</v>
       </c>
       <c r="B57" t="n">
-        <v>92675</v>
+        <v>92682</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>134374939</v>
       </c>
       <c r="B58" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 24660-2026 artfynd.xlsx
+++ b/artfynd/A 24660-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129520049</v>
+        <v>134374941</v>
       </c>
       <c r="B2" t="n">
-        <v>80187</v>
+        <v>92689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>898</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Froskdolpen, Froskdolpen, Jmt</t>
+          <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>390097</v>
+        <v>390512</v>
       </c>
       <c r="R2" t="n">
-        <v>7042178</v>
+        <v>7042352</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,60 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Nencia Mattsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nencia Mattsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129520071</v>
+        <v>134374942</v>
       </c>
       <c r="B3" t="n">
-        <v>80186</v>
+        <v>92689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Froskdolpen, Froskdolpen, Jmt</t>
+          <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>390180</v>
+        <v>390101</v>
       </c>
       <c r="R3" t="n">
-        <v>7042174</v>
+        <v>7041912</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Nencia Mattsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nencia Mattsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129519968</v>
+        <v>134374935</v>
       </c>
       <c r="B4" t="n">
-        <v>91619</v>
+        <v>91970</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,33 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Froskdolpen, Froskdolpen, Jmt</t>
+          <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>390109</v>
+        <v>390208</v>
       </c>
       <c r="R4" t="n">
-        <v>7042097</v>
+        <v>7041968</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -930,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -950,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Nencia Mattsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Nencia Mattsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134374888</v>
+        <v>134374856</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -973,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -997,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>390227</v>
+        <v>390407</v>
       </c>
       <c r="R5" t="n">
-        <v>7042198</v>
+        <v>7042260</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1033,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack (års)färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1064,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134374889</v>
+        <v>134374936</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1075,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>390050</v>
+        <v>390274</v>
       </c>
       <c r="R6" t="n">
-        <v>7042163</v>
+        <v>7042048</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1137,17 +1136,13 @@
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1166,10 +1161,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134374865</v>
+        <v>134374930</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>92406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1177,21 +1172,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1201,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>390261</v>
+        <v>390513</v>
       </c>
       <c r="R7" t="n">
-        <v>7042085</v>
+        <v>7042404</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1237,11 +1232,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1268,48 +1258,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134374860</v>
+        <v>129520049</v>
       </c>
       <c r="B8" t="n">
-        <v>92192</v>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Andtjärnen, Jmt</t>
+          <t>Froskdolpen, Froskdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>390227</v>
+        <v>390097</v>
       </c>
       <c r="R8" t="n">
-        <v>7042207</v>
+        <v>7042178</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1333,12 +1323,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1353,60 +1343,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Nencia Mattsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Nencia Mattsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134374858</v>
+        <v>129524739</v>
       </c>
       <c r="B9" t="n">
-        <v>92192</v>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andtjärnen, Jmt</t>
+          <t>Froskdolpen, Froskdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>390209</v>
+        <v>390379</v>
       </c>
       <c r="R9" t="n">
-        <v>7042023</v>
+        <v>7042426</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1430,12 +1420,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1450,22 +1440,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Nencia Mattsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Nencia Mattsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134374891</v>
+        <v>134374925</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>80489</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1473,21 +1463,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1497,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>390111</v>
+        <v>390411</v>
       </c>
       <c r="R10" t="n">
-        <v>7042033</v>
+        <v>7042114</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1533,11 +1523,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1564,10 +1549,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134374868</v>
+        <v>134374926</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>80489</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,21 +1560,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>390230</v>
+        <v>390354</v>
       </c>
       <c r="R11" t="n">
-        <v>7042154</v>
+        <v>7042406</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1635,11 +1620,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1666,10 +1646,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134374929</v>
+        <v>134374928</v>
       </c>
       <c r="B12" t="n">
-        <v>80482</v>
+        <v>80489</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1701,10 +1681,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>390092</v>
+        <v>390214</v>
       </c>
       <c r="R12" t="n">
-        <v>7042140</v>
+        <v>7042215</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,10 +1743,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134374887</v>
+        <v>134374929</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>80489</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1774,21 +1754,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1798,10 +1778,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>390245</v>
+        <v>390092</v>
       </c>
       <c r="R13" t="n">
-        <v>7042226</v>
+        <v>7042140</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1834,11 +1814,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1865,32 +1840,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134374935</v>
+        <v>134374857</v>
       </c>
       <c r="B14" t="n">
-        <v>91963</v>
+        <v>92199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1900,10 +1875,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>390208</v>
+        <v>390383</v>
       </c>
       <c r="R14" t="n">
-        <v>7041968</v>
+        <v>7042192</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1962,32 +1937,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134374869</v>
+        <v>134374858</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>92199</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1997,10 +1972,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>390166</v>
+        <v>390209</v>
       </c>
       <c r="R15" t="n">
-        <v>7042190</v>
+        <v>7042023</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,11 +2008,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2064,32 +2034,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134374928</v>
+        <v>134374859</v>
       </c>
       <c r="B16" t="n">
-        <v>80482</v>
+        <v>92199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2099,10 +2069,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>390214</v>
+        <v>390406</v>
       </c>
       <c r="R16" t="n">
-        <v>7042215</v>
+        <v>7042262</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2161,32 +2131,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134374940</v>
+        <v>134374860</v>
       </c>
       <c r="B17" t="n">
-        <v>79366</v>
+        <v>92199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2196,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>390093</v>
+        <v>390227</v>
       </c>
       <c r="R17" t="n">
-        <v>7042070</v>
+        <v>7042207</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2258,32 +2228,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134374890</v>
+        <v>134374861</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>92199</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2293,10 +2263,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>390089</v>
+        <v>390081</v>
       </c>
       <c r="R18" t="n">
-        <v>7042129</v>
+        <v>7041983</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,11 +2299,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2360,48 +2325,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134374942</v>
+        <v>129519531</v>
       </c>
       <c r="B19" t="n">
-        <v>92682</v>
+        <v>93233</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>898</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Andtjärnen, Jmt</t>
+          <t>Huvudstupmyren, Huvudstupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>390101</v>
+        <v>390210</v>
       </c>
       <c r="R19" t="n">
-        <v>7041912</v>
+        <v>7041753</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2425,12 +2390,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2445,65 +2410,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Nencia Mattsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Nencia Mattsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134374864</v>
+        <v>134374939</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>390255</v>
+        <v>390533</v>
       </c>
       <c r="R20" t="n">
-        <v>7042088</v>
+        <v>7042405</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2540,7 +2497,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Senare års bohål, ca 4,5m upp i död gran. Finns ytterligare 3 äldre bohål i samma träd, troligen av tretå.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2567,48 +2524,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129524739</v>
+        <v>134374940</v>
       </c>
       <c r="B21" t="n">
-        <v>80187</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Froskdolpen, Froskdolpen, Jmt</t>
+          <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>390379</v>
+        <v>390093</v>
       </c>
       <c r="R21" t="n">
-        <v>7042426</v>
+        <v>7042070</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2632,12 +2589,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2652,22 +2609,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Nencia Mattsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Nencia Mattsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129525037</v>
+        <v>129520071</v>
       </c>
       <c r="B22" t="n">
-        <v>79082</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2675,21 +2632,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2699,10 +2656,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>390406</v>
+        <v>390180</v>
       </c>
       <c r="R22" t="n">
-        <v>7042252</v>
+        <v>7042174</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2761,48 +2718,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129524728</v>
+        <v>134374931</v>
       </c>
       <c r="B23" t="n">
-        <v>80215</v>
+        <v>80488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Froskdolpen, Froskdolpen, Jmt</t>
+          <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>390386</v>
+        <v>390480</v>
       </c>
       <c r="R23" t="n">
-        <v>7042427</v>
+        <v>7042339</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2826,12 +2783,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2846,53 +2803,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Nencia Mattsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Nencia Mattsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129519780</v>
+        <v>129524728</v>
       </c>
       <c r="B24" t="n">
-        <v>91619</v>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Huvudstupmyren, Huvudstupmyren, Jmt</t>
+          <t>Froskdolpen, Froskdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>390313</v>
+        <v>390386</v>
       </c>
       <c r="R24" t="n">
-        <v>7041900</v>
+        <v>7042427</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2951,10 +2912,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129520094</v>
+        <v>129525085</v>
       </c>
       <c r="B25" t="n">
-        <v>79082</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2962,34 +2923,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>230405</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Froskdolpen, Froskdolpen, Jmt</t>
+          <t>Froskdolpen, Åre, Froskdolpen, Åre, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>390294</v>
+        <v>390273</v>
       </c>
       <c r="R25" t="n">
-        <v>7042149</v>
+        <v>7042247</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3022,6 +2983,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3048,10 +3014,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129524831</v>
+        <v>134374862</v>
       </c>
       <c r="B26" t="n">
-        <v>91619</v>
+        <v>57975</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3059,33 +3025,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Huvudstupmyren, Huvudstupmyren, Jmt</t>
+          <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>390545</v>
+        <v>390295</v>
       </c>
       <c r="R26" t="n">
-        <v>7042240</v>
+        <v>7041876</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3109,12 +3079,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3129,22 +3104,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Nencia Mattsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Nencia Mattsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129525085</v>
+        <v>134374863</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3172,17 +3147,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Froskdolpen, Åre, Froskdolpen, Åre, Jmt</t>
+          <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>390273</v>
+        <v>390316</v>
       </c>
       <c r="R27" t="n">
-        <v>7042247</v>
+        <v>7041877</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3206,17 +3181,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3231,19 +3206,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Nencia Mattsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Nencia Mattsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134374866</v>
+        <v>134374864</v>
       </c>
       <c r="B28" t="n">
         <v>57975</v>
@@ -3272,16 +3247,24 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>390422</v>
+        <v>390255</v>
       </c>
       <c r="R28" t="n">
-        <v>7042208</v>
+        <v>7042088</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3318,7 +3301,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Senare års bohål, ca 4,5m upp i död gran. Finns ytterligare 3 äldre bohål i samma träd, troligen av tretå.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3345,10 +3328,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134374856</v>
+        <v>134374865</v>
       </c>
       <c r="B29" t="n">
-        <v>91967</v>
+        <v>57975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3356,21 +3339,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3380,10 +3363,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>390407</v>
+        <v>390261</v>
       </c>
       <c r="R29" t="n">
-        <v>7042260</v>
+        <v>7042085</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3416,6 +3399,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3442,32 +3430,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134374859</v>
+        <v>134374866</v>
       </c>
       <c r="B30" t="n">
-        <v>92192</v>
+        <v>57975</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3477,10 +3465,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>390406</v>
+        <v>390422</v>
       </c>
       <c r="R30" t="n">
-        <v>7042262</v>
+        <v>7042208</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3513,6 +3501,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3539,7 +3532,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134374877</v>
+        <v>134374867</v>
       </c>
       <c r="B31" t="n">
         <v>57975</v>
@@ -3574,10 +3567,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>390321</v>
+        <v>390338</v>
       </c>
       <c r="R31" t="n">
-        <v>7042303</v>
+        <v>7042119</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3614,7 +3607,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3641,7 +3634,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134374867</v>
+        <v>134374868</v>
       </c>
       <c r="B32" t="n">
         <v>57975</v>
@@ -3676,10 +3669,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>390338</v>
+        <v>390230</v>
       </c>
       <c r="R32" t="n">
-        <v>7042119</v>
+        <v>7042154</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3716,7 +3709,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3743,32 +3736,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134374934</v>
+        <v>134374869</v>
       </c>
       <c r="B33" t="n">
-        <v>99092</v>
+        <v>57975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3778,10 +3771,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>390426</v>
+        <v>390166</v>
       </c>
       <c r="R33" t="n">
-        <v>7042146</v>
+        <v>7042190</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3814,6 +3807,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3840,10 +3838,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134374931</v>
+        <v>134374870</v>
       </c>
       <c r="B34" t="n">
-        <v>80481</v>
+        <v>57975</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3851,21 +3849,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3875,10 +3873,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>390480</v>
+        <v>390368</v>
       </c>
       <c r="R34" t="n">
-        <v>7042339</v>
+        <v>7041804</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3911,6 +3909,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3937,7 +3940,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134374883</v>
+        <v>134374871</v>
       </c>
       <c r="B35" t="n">
         <v>57975</v>
@@ -3972,10 +3975,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>390314</v>
+        <v>390476</v>
       </c>
       <c r="R35" t="n">
-        <v>7042226</v>
+        <v>7042050</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4012,7 +4015,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4039,7 +4042,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134374884</v>
+        <v>134374872</v>
       </c>
       <c r="B36" t="n">
         <v>57975</v>
@@ -4068,24 +4071,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>390326</v>
+        <v>390501</v>
       </c>
       <c r="R36" t="n">
-        <v>7042224</v>
+        <v>7042353</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4122,7 +4117,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Bohål, ca 4,5m upp i tajgagrantickerötad granhögstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4149,7 +4144,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134374872</v>
+        <v>134374873</v>
       </c>
       <c r="B37" t="n">
         <v>57975</v>
@@ -4178,16 +4173,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>390501</v>
+        <v>390461</v>
       </c>
       <c r="R37" t="n">
-        <v>7042353</v>
+        <v>7042459</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4224,7 +4227,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Bohål, ca 1,7m upp i granhögstubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4251,10 +4254,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134374925</v>
+        <v>134374874</v>
       </c>
       <c r="B38" t="n">
-        <v>80482</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4262,21 +4265,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4286,10 +4289,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>390411</v>
+        <v>390364</v>
       </c>
       <c r="R38" t="n">
-        <v>7042114</v>
+        <v>7042343</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4322,6 +4325,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4450,32 +4458,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134374923</v>
+        <v>134374876</v>
       </c>
       <c r="B40" t="n">
-        <v>99210</v>
+        <v>57975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4485,10 +4493,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>390426</v>
+        <v>390397</v>
       </c>
       <c r="R40" t="n">
-        <v>7042147</v>
+        <v>7042239</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4521,6 +4529,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4547,7 +4560,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134374874</v>
+        <v>134374877</v>
       </c>
       <c r="B41" t="n">
         <v>57975</v>
@@ -4582,10 +4595,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>390364</v>
+        <v>390321</v>
       </c>
       <c r="R41" t="n">
-        <v>7042343</v>
+        <v>7042303</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4649,7 +4662,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134374862</v>
+        <v>134374878</v>
       </c>
       <c r="B42" t="n">
         <v>57975</v>
@@ -4684,10 +4697,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>390295</v>
+        <v>390326</v>
       </c>
       <c r="R42" t="n">
-        <v>7041876</v>
+        <v>7042294</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4751,10 +4764,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134374926</v>
+        <v>134374881</v>
       </c>
       <c r="B43" t="n">
-        <v>80482</v>
+        <v>57975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4762,21 +4775,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4786,10 +4799,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>390354</v>
+        <v>390295</v>
       </c>
       <c r="R43" t="n">
-        <v>7042406</v>
+        <v>7042271</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4822,6 +4835,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4848,32 +4866,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134374930</v>
+        <v>134374882</v>
       </c>
       <c r="B44" t="n">
-        <v>92399</v>
+        <v>57975</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4883,10 +4901,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>390513</v>
+        <v>390307</v>
       </c>
       <c r="R44" t="n">
-        <v>7042404</v>
+        <v>7042259</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4919,6 +4937,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4945,7 +4968,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134374873</v>
+        <v>134374883</v>
       </c>
       <c r="B45" t="n">
         <v>57975</v>
@@ -4974,24 +4997,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>390461</v>
+        <v>390314</v>
       </c>
       <c r="R45" t="n">
-        <v>7042459</v>
+        <v>7042226</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5028,7 +5043,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Bohål, ca 1,7m upp i granhögstubbe</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5055,7 +5070,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134374886</v>
+        <v>134374884</v>
       </c>
       <c r="B46" t="n">
         <v>57975</v>
@@ -5084,16 +5099,24 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>390289</v>
+        <v>390326</v>
       </c>
       <c r="R46" t="n">
-        <v>7042175</v>
+        <v>7042224</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5130,7 +5153,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål, ca 4,5m upp i tajgagrantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5157,7 +5180,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134374876</v>
+        <v>134374885</v>
       </c>
       <c r="B47" t="n">
         <v>57975</v>
@@ -5192,10 +5215,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>390397</v>
+        <v>390325</v>
       </c>
       <c r="R47" t="n">
-        <v>7042239</v>
+        <v>7042168</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5259,32 +5282,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134374857</v>
+        <v>134374886</v>
       </c>
       <c r="B48" t="n">
-        <v>92192</v>
+        <v>57975</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5294,10 +5317,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>390383</v>
+        <v>390289</v>
       </c>
       <c r="R48" t="n">
-        <v>7042192</v>
+        <v>7042175</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5330,6 +5353,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5356,7 +5384,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134374878</v>
+        <v>134374887</v>
       </c>
       <c r="B49" t="n">
         <v>57975</v>
@@ -5391,10 +5419,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>390326</v>
+        <v>390245</v>
       </c>
       <c r="R49" t="n">
-        <v>7042294</v>
+        <v>7042226</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5431,7 +5459,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5458,7 +5486,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134374870</v>
+        <v>134374888</v>
       </c>
       <c r="B50" t="n">
         <v>57975</v>
@@ -5493,10 +5521,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>390368</v>
+        <v>390227</v>
       </c>
       <c r="R50" t="n">
-        <v>7041804</v>
+        <v>7042198</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5533,7 +5561,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack (års)färska och äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5560,7 +5588,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134374881</v>
+        <v>134374889</v>
       </c>
       <c r="B51" t="n">
         <v>57975</v>
@@ -5595,10 +5623,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>390295</v>
+        <v>390050</v>
       </c>
       <c r="R51" t="n">
-        <v>7042271</v>
+        <v>7042163</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5635,7 +5663,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5662,7 +5690,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134374882</v>
+        <v>134374890</v>
       </c>
       <c r="B52" t="n">
         <v>57975</v>
@@ -5697,10 +5725,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>390307</v>
+        <v>390089</v>
       </c>
       <c r="R52" t="n">
-        <v>7042259</v>
+        <v>7042129</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5737,7 +5765,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5764,7 +5792,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134374863</v>
+        <v>134374891</v>
       </c>
       <c r="B53" t="n">
         <v>57975</v>
@@ -5799,10 +5827,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>390316</v>
+        <v>390111</v>
       </c>
       <c r="R53" t="n">
-        <v>7041877</v>
+        <v>7042033</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5866,32 +5894,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134374871</v>
+        <v>134374934</v>
       </c>
       <c r="B54" t="n">
-        <v>57975</v>
+        <v>99099</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5901,10 +5929,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>390476</v>
+        <v>390426</v>
       </c>
       <c r="R54" t="n">
-        <v>7042050</v>
+        <v>7042146</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5937,11 +5965,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5968,32 +5991,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134374936</v>
+        <v>134374892</v>
       </c>
       <c r="B55" t="n">
-        <v>91967</v>
+        <v>109924</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>221184</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6003,10 +6026,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>390274</v>
+        <v>390075</v>
       </c>
       <c r="R55" t="n">
-        <v>7042048</v>
+        <v>7042146</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6047,7 +6070,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6066,32 +6088,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134374885</v>
+        <v>134374923</v>
       </c>
       <c r="B56" t="n">
-        <v>57975</v>
+        <v>99217</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6101,10 +6123,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>390325</v>
+        <v>390426</v>
       </c>
       <c r="R56" t="n">
-        <v>7042168</v>
+        <v>7042147</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6137,11 +6159,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6168,32 +6185,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134374941</v>
+        <v>134374932</v>
       </c>
       <c r="B57" t="n">
-        <v>92682</v>
+        <v>99472</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>898</v>
+        <v>222812</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6203,10 +6220,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>390512</v>
+        <v>390605</v>
       </c>
       <c r="R57" t="n">
-        <v>7042352</v>
+        <v>7042182</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6265,27 +6282,27 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134374939</v>
+        <v>129520094</v>
       </c>
       <c r="B58" t="n">
-        <v>79366</v>
+        <v>79328</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6296,17 +6313,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Andtjärnen, Jmt</t>
+          <t>Froskdolpen, Froskdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>390533</v>
+        <v>390294</v>
       </c>
       <c r="R58" t="n">
-        <v>7042405</v>
+        <v>7042149</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6330,17 +6347,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6355,15 +6367,112 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Nencia Mattsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Nencia Mattsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129525037</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Froskdolpen, Froskdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>390406</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7042252</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Nencia Mattsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Nencia Mattsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24660-2026 artfynd.xlsx
+++ b/artfynd/A 24660-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3014,7 +3014,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134374862</v>
+        <v>134374864</v>
       </c>
       <c r="B26" t="n">
         <v>57975</v>
@@ -3043,16 +3043,24 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>390295</v>
+        <v>390255</v>
       </c>
       <c r="R26" t="n">
-        <v>7041876</v>
+        <v>7042088</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3089,7 +3097,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Senare års bohål, ca 4,5m upp i död gran. Finns ytterligare 3 äldre bohål i samma träd, troligen av tretå.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3116,7 +3124,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134374863</v>
+        <v>134374873</v>
       </c>
       <c r="B27" t="n">
         <v>57975</v>
@@ -3145,16 +3153,24 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>390316</v>
+        <v>390461</v>
       </c>
       <c r="R27" t="n">
-        <v>7041877</v>
+        <v>7042459</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3191,7 +3207,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål, ca 1,7m upp i granhögstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3218,7 +3234,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134374864</v>
+        <v>134374884</v>
       </c>
       <c r="B28" t="n">
         <v>57975</v>
@@ -3261,10 +3277,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>390255</v>
+        <v>390326</v>
       </c>
       <c r="R28" t="n">
-        <v>7042088</v>
+        <v>7042224</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3301,7 +3317,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Senare års bohål, ca 4,5m upp i död gran. Finns ytterligare 3 äldre bohål i samma träd, troligen av tretå.</t>
+          <t>Bohål, ca 4,5m upp i tajgagrantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3328,32 +3344,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134374865</v>
+        <v>134374934</v>
       </c>
       <c r="B29" t="n">
-        <v>57975</v>
+        <v>99099</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3363,10 +3379,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>390261</v>
+        <v>390426</v>
       </c>
       <c r="R29" t="n">
-        <v>7042085</v>
+        <v>7042146</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3399,11 +3415,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3430,32 +3441,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134374866</v>
+        <v>134374892</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>109924</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>221184</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Torta</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactuca alpina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3465,10 +3476,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>390422</v>
+        <v>390075</v>
       </c>
       <c r="R30" t="n">
-        <v>7042208</v>
+        <v>7042146</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3501,11 +3512,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3532,32 +3538,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134374867</v>
+        <v>134374923</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>99217</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3567,10 +3573,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>390338</v>
+        <v>390426</v>
       </c>
       <c r="R31" t="n">
-        <v>7042119</v>
+        <v>7042147</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3603,11 +3609,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3634,32 +3635,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134374868</v>
+        <v>134374932</v>
       </c>
       <c r="B32" t="n">
-        <v>57975</v>
+        <v>99472</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>222812</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3669,10 +3670,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>390230</v>
+        <v>390605</v>
       </c>
       <c r="R32" t="n">
-        <v>7042154</v>
+        <v>7042182</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3705,11 +3706,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3736,48 +3732,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134374869</v>
+        <v>129520094</v>
       </c>
       <c r="B33" t="n">
-        <v>57975</v>
+        <v>79328</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>230405</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Andtjärnen, Jmt</t>
+          <t>Froskdolpen, Froskdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>390166</v>
+        <v>390294</v>
       </c>
       <c r="R33" t="n">
-        <v>7042190</v>
+        <v>7042149</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3801,17 +3797,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3826,60 +3817,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Nencia Mattsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Nencia Mattsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134374870</v>
+        <v>129525037</v>
       </c>
       <c r="B34" t="n">
-        <v>57975</v>
+        <v>79328</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>230405</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Andtjärnen, Jmt</t>
+          <t>Froskdolpen, Froskdolpen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>390368</v>
+        <v>390406</v>
       </c>
       <c r="R34" t="n">
-        <v>7041804</v>
+        <v>7042252</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3903,17 +3894,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3928,2551 +3914,15 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Nencia Mattsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Nencia Mattsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>134374871</v>
-      </c>
-      <c r="B35" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>390476</v>
-      </c>
-      <c r="R35" t="n">
-        <v>7042050</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>134374872</v>
-      </c>
-      <c r="B36" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>390501</v>
-      </c>
-      <c r="R36" t="n">
-        <v>7042353</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>134374873</v>
-      </c>
-      <c r="B37" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>390461</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7042459</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Bohål, ca 1,7m upp i granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>134374874</v>
-      </c>
-      <c r="B38" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>390364</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7042343</v>
-      </c>
-      <c r="S38" t="n">
-        <v>10</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>134374875</v>
-      </c>
-      <c r="B39" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>390409</v>
-      </c>
-      <c r="R39" t="n">
-        <v>7042310</v>
-      </c>
-      <c r="S39" t="n">
-        <v>10</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>134374876</v>
-      </c>
-      <c r="B40" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>390397</v>
-      </c>
-      <c r="R40" t="n">
-        <v>7042239</v>
-      </c>
-      <c r="S40" t="n">
-        <v>10</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>134374877</v>
-      </c>
-      <c r="B41" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>390321</v>
-      </c>
-      <c r="R41" t="n">
-        <v>7042303</v>
-      </c>
-      <c r="S41" t="n">
-        <v>10</v>
-      </c>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>134374878</v>
-      </c>
-      <c r="B42" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>390326</v>
-      </c>
-      <c r="R42" t="n">
-        <v>7042294</v>
-      </c>
-      <c r="S42" t="n">
-        <v>10</v>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>134374881</v>
-      </c>
-      <c r="B43" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>390295</v>
-      </c>
-      <c r="R43" t="n">
-        <v>7042271</v>
-      </c>
-      <c r="S43" t="n">
-        <v>10</v>
-      </c>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>134374882</v>
-      </c>
-      <c r="B44" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>390307</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7042259</v>
-      </c>
-      <c r="S44" t="n">
-        <v>10</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>134374883</v>
-      </c>
-      <c r="B45" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>390314</v>
-      </c>
-      <c r="R45" t="n">
-        <v>7042226</v>
-      </c>
-      <c r="S45" t="n">
-        <v>10</v>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>134374884</v>
-      </c>
-      <c r="B46" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>390326</v>
-      </c>
-      <c r="R46" t="n">
-        <v>7042224</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Bohål, ca 4,5m upp i tajgagrantickerötad granhögstubbe</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>134374885</v>
-      </c>
-      <c r="B47" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>390325</v>
-      </c>
-      <c r="R47" t="n">
-        <v>7042168</v>
-      </c>
-      <c r="S47" t="n">
-        <v>10</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>134374886</v>
-      </c>
-      <c r="B48" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>390289</v>
-      </c>
-      <c r="R48" t="n">
-        <v>7042175</v>
-      </c>
-      <c r="S48" t="n">
-        <v>10</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>134374887</v>
-      </c>
-      <c r="B49" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>390245</v>
-      </c>
-      <c r="R49" t="n">
-        <v>7042226</v>
-      </c>
-      <c r="S49" t="n">
-        <v>10</v>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>134374888</v>
-      </c>
-      <c r="B50" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>390227</v>
-      </c>
-      <c r="R50" t="n">
-        <v>7042198</v>
-      </c>
-      <c r="S50" t="n">
-        <v>10</v>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack (års)färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>134374889</v>
-      </c>
-      <c r="B51" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>390050</v>
-      </c>
-      <c r="R51" t="n">
-        <v>7042163</v>
-      </c>
-      <c r="S51" t="n">
-        <v>10</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>134374890</v>
-      </c>
-      <c r="B52" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>390089</v>
-      </c>
-      <c r="R52" t="n">
-        <v>7042129</v>
-      </c>
-      <c r="S52" t="n">
-        <v>10</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>134374891</v>
-      </c>
-      <c r="B53" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>390111</v>
-      </c>
-      <c r="R53" t="n">
-        <v>7042033</v>
-      </c>
-      <c r="S53" t="n">
-        <v>10</v>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>134374934</v>
-      </c>
-      <c r="B54" t="n">
-        <v>99099</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>220093</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Korallrot</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Corallorhiza trifida</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>390426</v>
-      </c>
-      <c r="R54" t="n">
-        <v>7042146</v>
-      </c>
-      <c r="S54" t="n">
-        <v>10</v>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AD54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>134374892</v>
-      </c>
-      <c r="B55" t="n">
-        <v>109924</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>221184</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Torta</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Lactuca alpina</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>390075</v>
-      </c>
-      <c r="R55" t="n">
-        <v>7042146</v>
-      </c>
-      <c r="S55" t="n">
-        <v>10</v>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AD55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>134374923</v>
-      </c>
-      <c r="B56" t="n">
-        <v>99217</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>221952</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Spindelblomster</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>390426</v>
-      </c>
-      <c r="R56" t="n">
-        <v>7042147</v>
-      </c>
-      <c r="S56" t="n">
-        <v>10</v>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AD56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>134374932</v>
-      </c>
-      <c r="B57" t="n">
-        <v>99472</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>222812</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Liljekonvalj</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Convallaria majalis</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Andtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>390605</v>
-      </c>
-      <c r="R57" t="n">
-        <v>7042182</v>
-      </c>
-      <c r="S57" t="n">
-        <v>10</v>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AA57" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="AD57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG57" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT57" t="inlineStr"/>
-      <c r="AW57" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>129520094</v>
-      </c>
-      <c r="B58" t="n">
-        <v>79328</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>230405</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Froskdolpen, Froskdolpen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>390294</v>
-      </c>
-      <c r="R58" t="n">
-        <v>7042149</v>
-      </c>
-      <c r="S58" t="n">
-        <v>5</v>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AD58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG58" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT58" t="inlineStr"/>
-      <c r="AW58" t="inlineStr">
-        <is>
-          <t>Nencia Mattsson</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>Nencia Mattsson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>129525037</v>
-      </c>
-      <c r="B59" t="n">
-        <v>79328</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>230405</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Froskdolpen, Froskdolpen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>390406</v>
-      </c>
-      <c r="R59" t="n">
-        <v>7042252</v>
-      </c>
-      <c r="S59" t="n">
-        <v>5</v>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="AD59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG59" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT59" t="inlineStr"/>
-      <c r="AW59" t="inlineStr">
-        <is>
-          <t>Nencia Mattsson</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>Nencia Mattsson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24660-2026 artfynd.xlsx
+++ b/artfynd/A 24660-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3014,7 +3014,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134374864</v>
+        <v>134374862</v>
       </c>
       <c r="B26" t="n">
         <v>57975</v>
@@ -3043,24 +3043,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>390255</v>
+        <v>390295</v>
       </c>
       <c r="R26" t="n">
-        <v>7042088</v>
+        <v>7041876</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3097,7 +3089,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Senare års bohål, ca 4,5m upp i död gran. Finns ytterligare 3 äldre bohål i samma träd, troligen av tretå.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3124,7 +3116,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134374873</v>
+        <v>134374863</v>
       </c>
       <c r="B27" t="n">
         <v>57975</v>
@@ -3153,24 +3145,16 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>390461</v>
+        <v>390316</v>
       </c>
       <c r="R27" t="n">
-        <v>7042459</v>
+        <v>7041877</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3207,7 +3191,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Bohål, ca 1,7m upp i granhögstubbe</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3234,7 +3218,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134374884</v>
+        <v>134374864</v>
       </c>
       <c r="B28" t="n">
         <v>57975</v>
@@ -3277,10 +3261,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>390326</v>
+        <v>390255</v>
       </c>
       <c r="R28" t="n">
-        <v>7042224</v>
+        <v>7042088</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3317,7 +3301,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Bohål, ca 4,5m upp i tajgagrantickerötad granhögstubbe</t>
+          <t>Senare års bohål, ca 4,5m upp i död gran. Finns ytterligare 3 äldre bohål i samma träd, troligen av tretå.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3344,32 +3328,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134374934</v>
+        <v>134374865</v>
       </c>
       <c r="B29" t="n">
-        <v>99099</v>
+        <v>57975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3379,10 +3363,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>390426</v>
+        <v>390261</v>
       </c>
       <c r="R29" t="n">
-        <v>7042146</v>
+        <v>7042085</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3415,6 +3399,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3441,32 +3430,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134374892</v>
+        <v>134374866</v>
       </c>
       <c r="B30" t="n">
-        <v>109924</v>
+        <v>57975</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221184</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Torta</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactuca alpina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3476,10 +3465,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>390075</v>
+        <v>390422</v>
       </c>
       <c r="R30" t="n">
-        <v>7042146</v>
+        <v>7042208</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3512,6 +3501,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3538,32 +3532,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134374923</v>
+        <v>134374867</v>
       </c>
       <c r="B31" t="n">
-        <v>99217</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3573,10 +3567,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>390426</v>
+        <v>390338</v>
       </c>
       <c r="R31" t="n">
-        <v>7042147</v>
+        <v>7042119</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3609,6 +3603,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3635,32 +3634,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134374932</v>
+        <v>134374868</v>
       </c>
       <c r="B32" t="n">
-        <v>99472</v>
+        <v>57975</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222812</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3670,10 +3669,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>390605</v>
+        <v>390230</v>
       </c>
       <c r="R32" t="n">
-        <v>7042182</v>
+        <v>7042154</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3706,6 +3705,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3732,48 +3736,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129520094</v>
+        <v>134374869</v>
       </c>
       <c r="B33" t="n">
-        <v>79328</v>
+        <v>57975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>230405</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Froskdolpen, Froskdolpen, Jmt</t>
+          <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>390294</v>
+        <v>390166</v>
       </c>
       <c r="R33" t="n">
-        <v>7042149</v>
+        <v>7042190</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3797,12 +3801,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3817,60 +3826,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Nencia Mattsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Nencia Mattsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129525037</v>
+        <v>134374870</v>
       </c>
       <c r="B34" t="n">
-        <v>79328</v>
+        <v>57975</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>230405</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Froskdolpen, Froskdolpen, Jmt</t>
+          <t>Andtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>390406</v>
+        <v>390368</v>
       </c>
       <c r="R34" t="n">
-        <v>7042252</v>
+        <v>7041804</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3894,12 +3903,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3914,15 +3928,2551 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134374871</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>390476</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7042050</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134374872</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>390501</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7042353</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134374873</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>390461</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7042459</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Bohål, ca 1,7m upp i granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134374874</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>390364</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7042343</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134374875</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>390409</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7042310</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134374876</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>390397</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7042239</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134374877</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>390321</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7042303</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>134374878</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>390326</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7042294</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134374881</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>390295</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7042271</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134374882</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>390307</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7042259</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134374883</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>390314</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7042226</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134374884</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>390326</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7042224</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Bohål, ca 4,5m upp i tajgagrantickerötad granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>134374885</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>390325</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7042168</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>134374886</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>390289</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7042175</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>134374887</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>390245</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7042226</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>134374888</v>
+      </c>
+      <c r="B50" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>390227</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7042198</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack (års)färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>134374889</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>390050</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7042163</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>134374890</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>390089</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7042129</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>134374891</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>390111</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7042033</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>134374934</v>
+      </c>
+      <c r="B54" t="n">
+        <v>99099</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>390426</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7042146</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>134374892</v>
+      </c>
+      <c r="B55" t="n">
+        <v>109924</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221184</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Torta</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lactuca alpina</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>390075</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7042146</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>134374923</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>390426</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7042147</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>134374932</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99472</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Andtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>390605</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7042182</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129520094</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Froskdolpen, Froskdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>390294</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7042149</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
           <t>Nencia Mattsson</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
+      <c r="AX58" t="inlineStr">
         <is>
           <t>Nencia Mattsson</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr"/>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129525037</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Froskdolpen, Froskdolpen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>390406</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7042252</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Nencia Mattsson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Nencia Mattsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24660-2026 artfynd.xlsx
+++ b/artfynd/A 24660-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AZ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374941</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374942</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374935</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374856</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374936</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374930</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129520049</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524739</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,6 +1591,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374925</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374926</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1740,6 +1795,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374928</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1837,6 +1897,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374929</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1934,6 +1999,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374857</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2031,6 +2101,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374858</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2128,6 +2203,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374859</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2225,6 +2305,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374860</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2322,6 +2407,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374861</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2419,6 +2509,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129519531</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2521,6 +2616,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374939</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2618,6 +2718,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374940</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2715,6 +2820,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129520071</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2812,6 +2922,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374931</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2909,6 +3024,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129524728</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3011,6 +3131,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129525085</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3113,6 +3238,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374862</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3215,6 +3345,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374863</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3325,6 +3460,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374864</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3427,6 +3567,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374865</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3529,6 +3674,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374866</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3631,6 +3781,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374867</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3733,6 +3888,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374868</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3835,6 +3995,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374869</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3937,6 +4102,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374870</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4039,6 +4209,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374871</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4141,6 +4316,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374872</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4251,6 +4431,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374873</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4353,6 +4538,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374874</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4455,6 +4645,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374875</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4557,6 +4752,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374876</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4659,6 +4859,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374877</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4761,6 +4966,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374878</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4863,6 +5073,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374881</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4965,6 +5180,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374882</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5067,6 +5287,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374883</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5177,6 +5402,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374884</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5279,6 +5509,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374885</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5381,6 +5616,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374886</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5483,6 +5723,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374887</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5585,6 +5830,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374888</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5687,6 +5937,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374889</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5789,6 +6044,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374890</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5891,6 +6151,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374891</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5988,6 +6253,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374934</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6085,6 +6355,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374892</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6182,6 +6457,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374923</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6279,6 +6559,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134374932</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6376,6 +6661,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129520094</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6473,8 +6763,73 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129525037</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 24660-2026 artfynd.xlsx
+++ b/artfynd/A 24660-2026 artfynd.xlsx
@@ -3142,7 +3142,7 @@
         <v>134374862</v>
       </c>
       <c r="B26" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3249,7 +3249,7 @@
         <v>134374863</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>134374865</v>
       </c>
       <c r="B29" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>134374866</v>
       </c>
       <c r="B30" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>134374867</v>
       </c>
       <c r="B31" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>134374868</v>
       </c>
       <c r="B32" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>134374869</v>
       </c>
       <c r="B33" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>134374870</v>
       </c>
       <c r="B34" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>134374871</v>
       </c>
       <c r="B35" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>134374872</v>
       </c>
       <c r="B36" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>134374874</v>
       </c>
       <c r="B38" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>134374875</v>
       </c>
       <c r="B39" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>134374876</v>
       </c>
       <c r="B40" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>134374877</v>
       </c>
       <c r="B41" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>134374878</v>
       </c>
       <c r="B42" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4977,7 +4977,7 @@
         <v>134374881</v>
       </c>
       <c r="B43" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>134374882</v>
       </c>
       <c r="B44" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         <v>134374883</v>
       </c>
       <c r="B45" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>134374885</v>
       </c>
       <c r="B47" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>134374886</v>
       </c>
       <c r="B48" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>134374887</v>
       </c>
       <c r="B49" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>134374888</v>
       </c>
       <c r="B50" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>134374889</v>
       </c>
       <c r="B51" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5948,7 +5948,7 @@
         <v>134374890</v>
       </c>
       <c r="B52" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         <v>134374891</v>
       </c>
       <c r="B53" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
